--- a/virtual-physics-lab/app/dl/HCI_Q3_torsion.xlsx
+++ b/virtual-physics-lab/app/dl/HCI_Q3_torsion.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +100,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -680,79 +681,79 @@
       <c r="A6" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>11.59</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>11.79</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>17.78</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>17.62</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>22.85</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>22.6</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>26.56</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>26.75</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>30.02</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>33.11</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>33.07</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -838,17 +839,17 @@
       <c r="A6" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>11.59</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>11.79</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>(B6+C6)/20</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>SIN(RADIANS(A6)/2)</f>
         <v/>
       </c>
@@ -857,7 +858,7 @@
           <t>gradient</t>
         </is>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>SLOPE(D6:D11,E6:E11)</f>
         <v/>
       </c>
@@ -871,17 +872,17 @@
       <c r="A7" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>17.78</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>17.62</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>(B7+C7)/20</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>SIN(RADIANS(A7)/2)</f>
         <v/>
       </c>
@@ -890,7 +891,7 @@
           <t>intercept</t>
         </is>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <f>INTERCEPT(D6:D11,E6:E11)</f>
         <v/>
       </c>
@@ -904,17 +905,17 @@
       <c r="A8" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>22.85</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>22.6</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>(B8+C8)/20</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>SIN(RADIANS(A8)/2)</f>
         <v/>
       </c>
@@ -923,8 +924,8 @@
           <t>k = m(2πC/gradient)²</t>
         </is>
       </c>
-      <c r="H8" s="7">
-        <f>0.068*(2*PI()*0.16399999999999998/SLOPE(D6:D11,E6:E11))^2</f>
+      <c r="H8" s="8">
+        <f>0.068*(2*PI()*0.164/SLOPE(D6:D11,E6:E11))^2</f>
         <v/>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -937,17 +938,17 @@
       <c r="A9" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>26.56</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>26.75</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>(B9+C9)/20</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>SIN(RADIANS(A9)/2)</f>
         <v/>
       </c>
@@ -956,17 +957,17 @@
       <c r="A10" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>29.99</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>30.02</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>(B10+C10)/20</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>SIN(RADIANS(A10)/2)</f>
         <v/>
       </c>
@@ -975,17 +976,17 @@
       <c r="A11" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>33.11</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>33.07</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>(B11+C11)/20</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>SIN(RADIANS(A11)/2)</f>
         <v/>
       </c>
